--- a/Result/21-06-25/NASDAQstock_21-06-25period252RS90.xlsx
+++ b/Result/21-06-25/NASDAQstock_21-06-25period252RS90.xlsx
@@ -3,33 +3,52 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <color rgb="FF008000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -39,12 +58,36 @@
       <color rgb="00008000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA500"/>
+        <bgColor rgb="FFFFA500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -65,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -92,6 +135,15 @@
       <left/>
       <right/>
       <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color rgb="00FF0000"/>
       </top>
       <bottom/>
@@ -100,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -111,9 +163,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -477,7 +536,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AP121"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -798,7 +857,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AJ2" s="9" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -827,7 +886,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>DASH</t>
         </is>
@@ -889,7 +948,7 @@
       <c r="U3" t="n">
         <v>8.888888888888888</v>
       </c>
-      <c r="V3" s="3" t="b">
+      <c r="V3" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W3" t="b">
@@ -933,7 +992,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr">
+      <c r="AJ3" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -962,7 +1021,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>GEV</t>
         </is>
@@ -1068,7 +1127,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr">
+      <c r="AJ4" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -1097,7 +1156,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
@@ -1203,7 +1262,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr">
+      <c r="AJ5" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -1232,7 +1291,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>CVNA</t>
         </is>
@@ -1338,7 +1397,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr">
+      <c r="AJ6" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -1367,7 +1426,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
@@ -1429,7 +1488,7 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="3" t="b">
+      <c r="V7" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="b">
@@ -1473,7 +1532,7 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="inlineStr">
+      <c r="AJ7" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -1608,7 +1667,7 @@
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="inlineStr">
+      <c r="AJ8" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -1637,7 +1696,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>CRS</t>
         </is>
@@ -1704,7 +1763,7 @@
       <c r="U9" t="n">
         <v>0.5555555555555555</v>
       </c>
-      <c r="V9" s="3" t="b">
+      <c r="V9" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="b">
@@ -1748,7 +1807,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ9" s="4" t="inlineStr">
+      <c r="AJ9" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -1777,7 +1836,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>CRDO</t>
         </is>
@@ -1886,7 +1945,7 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="AJ10" s="2" t="inlineStr">
+      <c r="AJ10" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -1915,7 +1974,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>GFI</t>
         </is>
@@ -2021,7 +2080,7 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AJ11" s="2" t="inlineStr">
+      <c r="AJ11" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -2050,7 +2109,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
@@ -2156,7 +2215,7 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AJ12" s="2" t="inlineStr">
+      <c r="AJ12" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -2185,7 +2244,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>EXEL</t>
         </is>
@@ -2291,7 +2350,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ13" s="2" t="inlineStr">
+      <c r="AJ13" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -2320,7 +2379,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>KGC</t>
         </is>
@@ -2426,7 +2485,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ14" s="2" t="inlineStr">
+      <c r="AJ14" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -2455,7 +2514,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>TOST</t>
         </is>
@@ -2563,7 +2622,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ15" s="2" t="inlineStr">
+      <c r="AJ15" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -2592,7 +2651,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>GILD</t>
         </is>
@@ -2654,7 +2713,7 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="3" t="b">
+      <c r="V16" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W16" t="b">
@@ -2698,7 +2757,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ16" s="2" t="inlineStr">
+      <c r="AJ16" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -2727,7 +2786,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>HIMS</t>
         </is>
@@ -2833,7 +2892,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ17" s="4" t="inlineStr">
+      <c r="AJ17" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -2862,7 +2921,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>RBRK</t>
         </is>
@@ -2968,7 +3027,7 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AJ18" s="2" t="inlineStr">
+      <c r="AJ18" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -2997,7 +3056,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
@@ -3103,7 +3162,7 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AJ19" s="2" t="inlineStr">
+      <c r="AJ19" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -3132,7 +3191,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>AEM</t>
         </is>
@@ -3238,7 +3297,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ20" s="2" t="inlineStr">
+      <c r="AJ20" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -3267,7 +3326,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>TWLO</t>
         </is>
@@ -3373,7 +3432,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ21" s="2" t="inlineStr">
+      <c r="AJ21" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -3514,7 +3573,7 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AJ22" s="4" t="inlineStr">
+      <c r="AJ22" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -3543,7 +3602,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>DUOL</t>
         </is>
@@ -3649,7 +3708,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ23" s="2" t="inlineStr">
+      <c r="AJ23" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -3678,7 +3737,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>RCL</t>
         </is>
@@ -3784,7 +3843,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ24" s="4" t="inlineStr">
+      <c r="AJ24" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -3813,7 +3872,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
@@ -3919,7 +3978,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ25" s="2" t="inlineStr">
+      <c r="AJ25" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -3948,7 +4007,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>CW</t>
         </is>
@@ -4010,7 +4069,7 @@
       <c r="U26" t="n">
         <v>30</v>
       </c>
-      <c r="V26" s="3" t="b">
+      <c r="V26" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W26" t="b">
@@ -4054,7 +4113,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ26" s="4" t="inlineStr">
+      <c r="AJ26" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -4083,7 +4142,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>WPM</t>
         </is>
@@ -4145,7 +4204,7 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="3" t="b">
+      <c r="V27" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W27" t="b">
@@ -4189,7 +4248,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ27" s="2" t="inlineStr">
+      <c r="AJ27" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -4218,7 +4277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>HWM</t>
         </is>
@@ -4280,7 +4339,7 @@
       <c r="U28" t="n">
         <v>12.22222222222222</v>
       </c>
-      <c r="V28" s="3" t="b">
+      <c r="V28" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W28" t="b">
@@ -4324,7 +4383,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ28" s="4" t="inlineStr">
+      <c r="AJ28" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -4459,7 +4518,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ29" s="4" t="inlineStr">
+      <c r="AJ29" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -4594,7 +4653,7 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AJ30" s="4" t="inlineStr">
+      <c r="AJ30" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -4623,7 +4682,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>NRG</t>
         </is>
@@ -4685,7 +4744,7 @@
       <c r="U31" t="n">
         <v>19.44444444444445</v>
       </c>
-      <c r="V31" s="3" t="b">
+      <c r="V31" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W31" t="b">
@@ -4729,7 +4788,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ31" s="4" t="inlineStr">
+      <c r="AJ31" s="11" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
@@ -4864,7 +4923,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ32" s="4" t="inlineStr">
+      <c r="AJ32" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -4999,7 +5058,7 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AJ33" s="4" t="inlineStr">
+      <c r="AJ33" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -5063,7 +5122,7 @@
       <c r="K34" t="n">
         <v>1.67</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="L34" s="13" t="n">
         <v>-1.11993179549393</v>
       </c>
       <c r="M34" t="n">
@@ -5134,7 +5193,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ34" s="2" t="inlineStr">
+      <c r="AJ34" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -5163,7 +5222,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
@@ -5225,7 +5284,7 @@
       <c r="U35" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="V35" s="3" t="b">
+      <c r="V35" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W35" t="b">
@@ -5269,7 +5328,7 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AJ35" s="4" t="inlineStr">
+      <c r="AJ35" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -5298,7 +5357,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
@@ -5360,7 +5419,7 @@
       <c r="U36" t="n">
         <v>9.444444444444443</v>
       </c>
-      <c r="V36" s="3" t="b">
+      <c r="V36" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W36" t="b">
@@ -5404,7 +5463,7 @@
           <t>2025-07-18</t>
         </is>
       </c>
-      <c r="AJ36" s="2" t="inlineStr">
+      <c r="AJ36" s="9" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -5495,7 +5554,7 @@
       <c r="U37" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="3" t="b">
+      <c r="V37" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W37" t="b">
@@ -5539,7 +5598,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ37" s="2" t="inlineStr">
+      <c r="AJ37" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -5674,7 +5733,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ38" s="4" t="inlineStr">
+      <c r="AJ38" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -5703,7 +5762,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>BROS</t>
         </is>
@@ -5809,7 +5868,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ39" s="4" t="inlineStr">
+      <c r="AJ39" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -5838,7 +5897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
@@ -5900,7 +5959,7 @@
       <c r="U40" t="n">
         <v>11.11111111111111</v>
       </c>
-      <c r="V40" s="3" t="b">
+      <c r="V40" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W40" t="b">
@@ -5944,7 +6003,7 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AJ40" s="4" t="inlineStr">
+      <c r="AJ40" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -5973,7 +6032,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>BCS</t>
         </is>
@@ -6035,7 +6094,7 @@
       <c r="U41" t="n">
         <v>7.222222222222221</v>
       </c>
-      <c r="V41" s="3" t="b">
+      <c r="V41" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W41" t="b">
@@ -6079,7 +6138,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ41" s="4" t="inlineStr">
+      <c r="AJ41" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -6108,7 +6167,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>NWG</t>
         </is>
@@ -6208,7 +6267,7 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AJ42" s="4" t="inlineStr">
+      <c r="AJ42" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -6299,7 +6358,7 @@
       <c r="U43" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="V43" s="3" t="b">
+      <c r="V43" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W43" t="b">
@@ -6337,7 +6396,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ43" s="4" t="inlineStr">
+      <c r="AJ43" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -6366,7 +6425,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>JBL</t>
         </is>
@@ -6425,7 +6484,7 @@
       <c r="S44" t="n">
         <v>1.11</v>
       </c>
-      <c r="T44" s="6" t="inlineStr">
+      <c r="T44" s="13" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -6483,7 +6542,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ44" s="2" t="inlineStr">
+      <c r="AJ44" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -6512,7 +6571,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>SPOT</t>
         </is>
@@ -6574,7 +6633,7 @@
       <c r="U45" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="3" t="b">
+      <c r="V45" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W45" t="b">
@@ -6618,7 +6677,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ45" s="2" t="inlineStr">
+      <c r="AJ45" s="9" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -6647,7 +6706,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
@@ -6682,7 +6741,7 @@
       <c r="K46" t="n">
         <v>1.56</v>
       </c>
-      <c r="L46" s="6" t="n">
+      <c r="L46" s="13" t="n">
         <v>-1.17978240156891</v>
       </c>
       <c r="M46" t="n">
@@ -6709,7 +6768,7 @@
       <c r="U46" t="n">
         <v>2.777777777777778</v>
       </c>
-      <c r="V46" s="3" t="b">
+      <c r="V46" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W46" t="b">
@@ -6753,7 +6812,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ46" s="4" t="inlineStr">
+      <c r="AJ46" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -6782,7 +6841,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>FFIV</t>
         </is>
@@ -6844,7 +6903,7 @@
       <c r="U47" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="b">
+      <c r="V47" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W47" t="b">
@@ -6888,7 +6947,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ47" s="2" t="inlineStr">
+      <c r="AJ47" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -6917,7 +6976,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>IBKR</t>
         </is>
@@ -6979,7 +7038,7 @@
       <c r="U48" t="n">
         <v>12.22222222222222</v>
       </c>
-      <c r="V48" s="3" t="b">
+      <c r="V48" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W48" t="b">
@@ -7023,7 +7082,7 @@
           <t>2025-07-14</t>
         </is>
       </c>
-      <c r="AJ48" s="4" t="inlineStr">
+      <c r="AJ48" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -7087,7 +7146,7 @@
       <c r="K49" t="n">
         <v>1.59</v>
       </c>
-      <c r="L49" s="6" t="n">
+      <c r="L49" s="13" t="n">
         <v>-1.163459509003006</v>
       </c>
       <c r="M49" t="n">
@@ -7114,7 +7173,7 @@
       <c r="U49" t="n">
         <v>2.222222222222222</v>
       </c>
-      <c r="V49" s="3" t="b">
+      <c r="V49" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W49" t="b">
@@ -7164,7 +7223,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ49" s="4" t="inlineStr">
+      <c r="AJ49" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -7255,7 +7314,7 @@
       <c r="U50" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="3" t="b">
+      <c r="V50" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W50" t="b">
@@ -7299,7 +7358,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ50" s="2" t="inlineStr">
+      <c r="AJ50" s="9" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -7363,7 +7422,7 @@
       <c r="K51" t="n">
         <v>1.85</v>
       </c>
-      <c r="L51" s="6" t="n">
+      <c r="L51" s="13" t="n">
         <v>-1.02199444009851</v>
       </c>
       <c r="M51" t="n">
@@ -7390,7 +7449,7 @@
       <c r="U51" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="V51" s="3" t="b">
+      <c r="V51" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W51" t="b">
@@ -7434,7 +7493,7 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AJ51" s="2" t="inlineStr">
+      <c r="AJ51" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -7463,7 +7522,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>ULS</t>
         </is>
@@ -7525,7 +7584,7 @@
       <c r="U52" t="n">
         <v>4.444444444444444</v>
       </c>
-      <c r="V52" s="3" t="b">
+      <c r="V52" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W52" t="b">
@@ -7569,7 +7628,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ52" s="4" t="inlineStr">
+      <c r="AJ52" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -7598,7 +7657,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>RBLX</t>
         </is>
@@ -7704,7 +7763,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ53" s="2" t="inlineStr">
+      <c r="AJ53" s="9" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -7733,7 +7792,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>SRAD</t>
         </is>
@@ -7841,7 +7900,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ54" s="2" t="inlineStr">
+      <c r="AJ54" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -7976,7 +8035,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ55" s="4" t="inlineStr">
+      <c r="AJ55" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -8111,7 +8170,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ56" s="2" t="inlineStr">
+      <c r="AJ56" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -8169,13 +8228,13 @@
       <c r="I57" t="n">
         <v>0.2</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="J57" s="13" t="n">
         <v>-1.426619289293619</v>
       </c>
       <c r="K57" t="n">
         <v>0.55</v>
       </c>
-      <c r="L57" s="6" t="n">
+      <c r="L57" s="13" t="n">
         <v>-1.729319784620992</v>
       </c>
       <c r="M57" t="n">
@@ -8202,7 +8261,7 @@
       <c r="U57" t="n">
         <v>2.777777777777778</v>
       </c>
-      <c r="V57" s="3" t="b">
+      <c r="V57" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W57" t="b">
@@ -8246,7 +8305,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ57" s="4" t="inlineStr">
+      <c r="AJ57" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -8337,7 +8396,7 @@
       <c r="U58" t="n">
         <v>1.111111111111111</v>
       </c>
-      <c r="V58" s="3" t="b">
+      <c r="V58" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W58" t="b">
@@ -8387,7 +8446,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ58" s="2" t="inlineStr">
+      <c r="AJ58" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -8416,7 +8475,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>AVPT</t>
         </is>
@@ -8522,7 +8581,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ59" s="2" t="inlineStr">
+      <c r="AJ59" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -8551,7 +8610,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>GRND</t>
         </is>
@@ -8613,7 +8672,7 @@
       <c r="U60" t="n">
         <v>12.77777777777778</v>
       </c>
-      <c r="V60" s="3" t="b">
+      <c r="V60" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W60" t="b">
@@ -8657,7 +8716,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ60" s="2" t="inlineStr">
+      <c r="AJ60" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -8721,7 +8780,7 @@
       <c r="K61" t="n">
         <v>8.140000000000001</v>
       </c>
-      <c r="L61" s="5" t="n">
+      <c r="L61" s="12" t="n">
         <v>2.400372034552579</v>
       </c>
       <c r="M61" t="n">
@@ -8792,7 +8851,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ61" s="4" t="inlineStr">
+      <c r="AJ61" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -8927,7 +8986,7 @@
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="AJ62" s="4" t="inlineStr">
+      <c r="AJ62" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -8956,7 +9015,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>PBI</t>
         </is>
@@ -9018,7 +9077,7 @@
       <c r="U63" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="3" t="b">
+      <c r="V63" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W63" t="b">
@@ -9062,7 +9121,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ63" s="4" t="inlineStr">
+      <c r="AJ63" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -9199,7 +9258,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ64" s="2" t="inlineStr">
+      <c r="AJ64" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -9228,7 +9287,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>MVST</t>
         </is>
@@ -9257,13 +9316,13 @@
       <c r="I65" t="n">
         <v>6.59</v>
       </c>
-      <c r="J65" s="5" t="n">
+      <c r="J65" s="12" t="n">
         <v>2.494844974508887</v>
       </c>
       <c r="K65" t="n">
         <v>8.15</v>
       </c>
-      <c r="L65" s="5" t="n">
+      <c r="L65" s="12" t="n">
         <v>2.405812998741213</v>
       </c>
       <c r="M65" t="n">
@@ -9334,7 +9393,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ65" s="4" t="inlineStr">
+      <c r="AJ65" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -9469,7 +9528,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ66" s="2" t="inlineStr">
+      <c r="AJ66" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -9498,7 +9557,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>ROAD</t>
         </is>
@@ -9604,7 +9663,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ67" s="4" t="inlineStr">
+      <c r="AJ67" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -9739,7 +9798,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ68" s="4" t="inlineStr">
+      <c r="AJ68" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -9768,7 +9827,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>LIF</t>
         </is>
@@ -9874,7 +9933,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ69" s="2" t="inlineStr">
+      <c r="AJ69" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -10009,7 +10068,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ70" s="2" t="inlineStr">
+      <c r="AJ70" s="9" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -10038,7 +10097,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="12" t="inlineStr">
         <is>
           <t>PEGA</t>
         </is>
@@ -10100,7 +10159,7 @@
       <c r="U71" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="V71" s="3" t="b">
+      <c r="V71" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W71" t="b">
@@ -10144,7 +10203,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ71" s="2" t="inlineStr">
+      <c r="AJ71" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -10279,7 +10338,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ72" s="2" t="inlineStr">
+      <c r="AJ72" s="9" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -10308,7 +10367,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="12" t="inlineStr">
         <is>
           <t>BCRX</t>
         </is>
@@ -10414,7 +10473,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ73" s="2" t="inlineStr">
+      <c r="AJ73" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -10478,7 +10537,7 @@
       <c r="K74" t="n">
         <v>1.87</v>
       </c>
-      <c r="L74" s="6" t="n">
+      <c r="L74" s="13" t="n">
         <v>-1.011112511721241</v>
       </c>
       <c r="M74" t="n">
@@ -10505,7 +10564,7 @@
       <c r="U74" t="n">
         <v>0.5555555555555555</v>
       </c>
-      <c r="V74" s="3" t="b">
+      <c r="V74" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W74" t="b">
@@ -10543,7 +10602,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ74" s="4" t="inlineStr">
+      <c r="AJ74" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -10678,7 +10737,7 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AJ75" s="4" t="inlineStr">
+      <c r="AJ75" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -10742,7 +10801,7 @@
       <c r="K76" t="n">
         <v>10.35</v>
       </c>
-      <c r="L76" s="5" t="n">
+      <c r="L76" s="12" t="n">
         <v>3.602825120240798</v>
       </c>
       <c r="M76" t="n">
@@ -10813,7 +10872,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ76" s="2" t="inlineStr">
+      <c r="AJ76" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -10948,7 +11007,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ77" s="2" t="inlineStr">
+      <c r="AJ77" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -11083,7 +11142,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ78" s="4" t="inlineStr">
+      <c r="AJ78" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -11112,7 +11171,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>BTSG</t>
         </is>
@@ -11218,7 +11277,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ79" s="2" t="inlineStr">
+      <c r="AJ79" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -11353,7 +11412,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ80" s="2" t="inlineStr">
+      <c r="AJ80" s="9" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -11494,7 +11553,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ81" s="2" t="inlineStr">
+      <c r="AJ81" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -11523,7 +11582,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="12" t="inlineStr">
         <is>
           <t>OLO</t>
         </is>
@@ -11629,7 +11688,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ82" s="2" t="inlineStr">
+      <c r="AJ82" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -11775,7 +11834,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ83" s="2" t="inlineStr">
+      <c r="AJ83" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -11916,7 +11975,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ84" s="4" t="inlineStr">
+      <c r="AJ84" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -12051,7 +12110,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ85" s="4" t="inlineStr">
+      <c r="AJ85" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -12109,7 +12168,7 @@
       <c r="I86" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="J86" s="5" t="n">
+      <c r="J86" s="12" t="n">
         <v>3.685399070248615</v>
       </c>
       <c r="K86" t="n">
@@ -12186,7 +12245,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ86" s="4" t="inlineStr">
+      <c r="AJ86" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -12277,7 +12336,7 @@
       <c r="U87" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="3" t="b">
+      <c r="V87" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W87" t="b">
@@ -12321,7 +12380,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ87" s="2" t="inlineStr">
+      <c r="AJ87" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -12350,7 +12409,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="12" t="inlineStr">
         <is>
           <t>CHEF</t>
         </is>
@@ -12412,7 +12471,7 @@
       <c r="U88" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="3" t="b">
+      <c r="V88" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W88" t="b">
@@ -12456,7 +12515,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ88" s="4" t="inlineStr">
+      <c r="AJ88" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -12591,7 +12650,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ89" s="2" t="inlineStr">
+      <c r="AJ89" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -12620,7 +12679,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="12" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
@@ -12682,7 +12741,7 @@
       <c r="U90" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="3" t="b">
+      <c r="V90" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W90" t="b">
@@ -12726,7 +12785,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ90" s="2" t="inlineStr">
+      <c r="AJ90" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -12755,7 +12814,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>QBTS</t>
         </is>
@@ -12784,13 +12843,13 @@
       <c r="I91" t="n">
         <v>7.46</v>
       </c>
-      <c r="J91" s="5" t="n">
+      <c r="J91" s="12" t="n">
         <v>3.028753254557115</v>
       </c>
       <c r="K91" t="n">
         <v>9.77</v>
       </c>
-      <c r="L91" s="5" t="n">
+      <c r="L91" s="12" t="n">
         <v>3.287249197299998</v>
       </c>
       <c r="M91" t="n">
@@ -12861,7 +12920,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ91" s="2" t="inlineStr">
+      <c r="AJ91" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -12890,7 +12949,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>AGX</t>
         </is>
@@ -12996,7 +13055,7 @@
           <t>2025-09-04</t>
         </is>
       </c>
-      <c r="AJ92" s="4" t="inlineStr">
+      <c r="AJ92" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -13131,7 +13190,7 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="AJ93" s="4" t="inlineStr">
+      <c r="AJ93" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -13160,7 +13219,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>ATGE</t>
         </is>
@@ -13266,7 +13325,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ94" s="4" t="inlineStr">
+      <c r="AJ94" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -13357,7 +13416,7 @@
       <c r="U95" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="3" t="b">
+      <c r="V95" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W95" t="b">
@@ -13401,7 +13460,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ95" s="2" t="inlineStr">
+      <c r="AJ95" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -13492,7 +13551,7 @@
       <c r="U96" t="n">
         <v>3.888888888888888</v>
       </c>
-      <c r="V96" s="3" t="b">
+      <c r="V96" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W96" t="b">
@@ -13536,7 +13595,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ96" s="4" t="inlineStr">
+      <c r="AJ96" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -13594,13 +13653,13 @@
       <c r="I97" t="n">
         <v>0.59</v>
       </c>
-      <c r="J97" s="6" t="n">
+      <c r="J97" s="13" t="n">
         <v>-1.187281094789241</v>
       </c>
       <c r="K97" t="n">
         <v>0.43</v>
       </c>
-      <c r="L97" s="6" t="n">
+      <c r="L97" s="13" t="n">
         <v>-1.794611354884606</v>
       </c>
       <c r="M97" t="n">
@@ -13627,7 +13686,7 @@
       <c r="U97" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="3" t="b">
+      <c r="V97" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W97" t="b">
@@ -13671,7 +13730,7 @@
           <t>2025-08-26</t>
         </is>
       </c>
-      <c r="AJ97" s="2" t="inlineStr">
+      <c r="AJ97" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -13700,7 +13759,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" s="12" t="inlineStr">
         <is>
           <t>UTI</t>
         </is>
@@ -13806,7 +13865,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ98" s="4" t="inlineStr">
+      <c r="AJ98" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -13835,7 +13894,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" s="12" t="inlineStr">
         <is>
           <t>TPB</t>
         </is>
@@ -13897,7 +13956,7 @@
       <c r="U99" t="n">
         <v>6.111111111111111</v>
       </c>
-      <c r="V99" s="3" t="b">
+      <c r="V99" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W99" t="b">
@@ -13941,7 +14000,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ99" s="4" t="inlineStr">
+      <c r="AJ99" s="11" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -13970,7 +14029,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" s="12" t="inlineStr">
         <is>
           <t>ESE</t>
         </is>
@@ -14032,7 +14091,7 @@
       <c r="U100" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="b">
+      <c r="V100" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W100" t="b">
@@ -14076,7 +14135,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ100" s="2" t="inlineStr">
+      <c r="AJ100" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -14211,7 +14270,7 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="AJ101" s="4" t="inlineStr">
+      <c r="AJ101" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -14302,7 +14361,7 @@
       <c r="U102" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="b">
+      <c r="V102" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W102" t="b">
@@ -14346,7 +14405,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ102" s="4" t="inlineStr">
+      <c r="AJ102" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -14410,7 +14469,7 @@
       <c r="K103" t="n">
         <v>1.59</v>
       </c>
-      <c r="L103" s="6" t="n">
+      <c r="L103" s="13" t="n">
         <v>-1.163459509003006</v>
       </c>
       <c r="M103" t="n">
@@ -14437,7 +14496,7 @@
       <c r="U103" t="n">
         <v>2.222222222222222</v>
       </c>
-      <c r="V103" s="3" t="b">
+      <c r="V103" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W103" t="b">
@@ -14487,7 +14546,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ103" s="2" t="inlineStr">
+      <c r="AJ103" s="9" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -14622,7 +14681,7 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AJ104" s="4" t="inlineStr">
+      <c r="AJ104" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -14760,7 +14819,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ105" s="4" t="inlineStr">
+      <c r="AJ105" s="11" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -14789,7 +14848,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="A106" s="12" t="inlineStr">
         <is>
           <t>ODD</t>
         </is>
@@ -14895,7 +14954,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ106" s="2" t="inlineStr">
+      <c r="AJ106" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -15030,7 +15089,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ107" s="4" t="inlineStr">
+      <c r="AJ107" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -15165,7 +15224,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ108" s="4" t="inlineStr">
+      <c r="AJ108" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -15300,7 +15359,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ109" s="2" t="inlineStr">
+      <c r="AJ109" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -15329,7 +15388,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="A110" s="12" t="inlineStr">
         <is>
           <t>ZLAB</t>
         </is>
@@ -15435,7 +15494,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ110" s="2" t="inlineStr">
+      <c r="AJ110" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -15575,7 +15634,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ111" s="4" t="inlineStr">
+      <c r="AJ111" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -15604,7 +15663,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="A112" s="12" t="inlineStr">
         <is>
           <t>EE</t>
         </is>
@@ -15710,7 +15769,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ112" s="2" t="inlineStr">
+      <c r="AJ112" s="9" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -15845,7 +15904,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ113" s="4" t="inlineStr">
+      <c r="AJ113" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -15936,7 +15995,7 @@
       <c r="U114" t="n">
         <v>5</v>
       </c>
-      <c r="V114" s="3" t="b">
+      <c r="V114" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W114" t="b">
@@ -15980,7 +16039,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ114" s="4" t="inlineStr">
+      <c r="AJ114" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -16038,7 +16097,7 @@
       <c r="I115" t="n">
         <v>7.2</v>
       </c>
-      <c r="J115" s="5" t="n">
+      <c r="J115" s="12" t="n">
         <v>2.869194458220863</v>
       </c>
       <c r="K115" t="n">
@@ -16121,7 +16180,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ115" s="2" t="inlineStr">
+      <c r="AJ115" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -16179,13 +16238,13 @@
       <c r="I116" t="n">
         <v>9.91</v>
       </c>
-      <c r="J116" s="5" t="n">
+      <c r="J116" s="12" t="n">
         <v>4.532288066187185</v>
       </c>
       <c r="K116" t="n">
         <v>11.54</v>
       </c>
-      <c r="L116" s="5" t="n">
+      <c r="L116" s="12" t="n">
         <v>4.250299858688301</v>
       </c>
       <c r="M116" t="n">
@@ -16256,7 +16315,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ116" s="2" t="inlineStr">
+      <c r="AJ116" s="9" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -16314,7 +16373,7 @@
       <c r="I117" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="J117" s="5" t="n">
+      <c r="J117" s="12" t="n">
         <v>3.599482795298326</v>
       </c>
       <c r="K117" t="n">
@@ -16397,7 +16456,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ117" s="4" t="inlineStr">
+      <c r="AJ117" s="11" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -16426,7 +16485,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="A118" s="12" t="inlineStr">
         <is>
           <t>CCB</t>
         </is>
@@ -16532,7 +16591,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ118" s="4" t="inlineStr">
+      <c r="AJ118" s="11" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -16623,7 +16682,7 @@
       <c r="U119" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="V119" s="3" t="b">
+      <c r="V119" s="10" t="b">
         <v>1</v>
       </c>
       <c r="W119" t="b">
@@ -16667,7 +16726,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ119" s="2" t="inlineStr">
+      <c r="AJ119" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -16725,13 +16784,13 @@
       <c r="I120" t="n">
         <v>6.36</v>
       </c>
-      <c r="J120" s="5" t="n">
+      <c r="J120" s="12" t="n">
         <v>2.353696808519126</v>
       </c>
       <c r="K120" t="n">
         <v>7.88</v>
       </c>
-      <c r="L120" s="5" t="n">
+      <c r="L120" s="12" t="n">
         <v>2.258906965648082</v>
       </c>
       <c r="M120" t="n">
@@ -16802,7 +16861,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ120" s="2" t="inlineStr">
+      <c r="AJ120" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -16940,7 +16999,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ121" s="2" t="inlineStr">
+      <c r="AJ121" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
